--- a/바통/돌다리/모의데이터/정답표.xlsx
+++ b/바통/돌다리/모의데이터/정답표.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정답" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파일목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>연번</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -430,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>내용</t>
+          <t>요약</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -440,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>출처 파일</t>
+          <t>파일</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>출처 위치</t>
+          <t>위치</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -465,7 +464,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3월 20일까지 부서 소모품 수요 취합 후 상반기 구매 계획 수립</t>
+          <t>관내국 협조 : 국별 목표를 3월 14일까지 배정하고 분기별 진도점검 회의 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -475,17 +474,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01_공문/03_행정지원과1023_2025년_상반기_소모품_구매_계획_수립.hwpx</t>
+          <t>01_공문/01_영업과412_202503_2025년_우편매출액_목표_달성_세부추진계획_수립.odt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부서 소모품 수요를 3월 20일까지 취합하여 상반기 구매 계획을 수립합니다.</t>
+          <t>라. 관내국 협조 : 국별 목표를 3월 14일까지 배정하고 분기별 진도점검 회의 개최</t>
         </is>
       </c>
     </row>
@@ -495,28 +494,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>강민재 · 한빛군청 재정과 예산담당 · 063-000-0101 · 예산 편성·추경 협의</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>계약 갱신을 원하시면 5월 30일까지 요금후납 계약 갱신 신청서를 제출하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025년 4월</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01_공문/03_행정지원과1023_2025년_상반기_소모품_구매_계획_수립.hwpx</t>
+          <t>01_공문/02_영업과603_202504_요금후납_우편물_발송_계약_갱신_안내.odt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강민재(한빛군청 재정과 예산담당, 063-000-0101)</t>
+          <t>3. 계약 갱신을 원하시면 5월 30일까지 요금후납 계약 갱신 신청서를 제출하여 주시기 바랍니다.</t>
         </is>
       </c>
     </row>
@@ -531,27 +534,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4월 셋째 주 소방안전점검 실시, 지적사항 4월 30일까지 조치</t>
+          <t>협의결과 : 6월 중 우체국쇼핑 입점 심사 신청, 심사 서류는 업체가 6월 13일까지 제출</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025년 4월</t>
+          <t>2025년 5월</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01_공문/04_행정지원과1388_2025년_청사_소방안전점검_실시_계획.hwpx</t>
+          <t>01_공문/04_영업과812_202505_우체국쇼핑_지역특산품_입점_협의_결과_보고.odt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4월 셋째 주에 한빛소방서 입회 아래 청사 소방안전점검을 실시합니다.</t>
+          <t>다. 협의결과 : 6월 중 우체국쇼핑 입점 심사 신청, 심사 서류는 업체가 6월 13일까지 제출</t>
         </is>
       </c>
     </row>
@@ -561,28 +564,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>박도윤 · 한빛소방서 예방안전과 · 063-000-0303 · 소방안전점검 입회</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>준비사항 : 국별 상반기 실적과 하반기 추진계획을 7월 18일까지 영업과로 제출</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025년 7월</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01_공문/04_행정지원과1388_2025년_청사_소방안전점검_실시_계획.hwpx</t>
+          <t>01_공문/05_영업과1240_202507_2025년_하반기_우편매출_진도점검_회의_개최_알림.odt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>박도윤(한빛소방서 예방안전과, 063-000-0303)</t>
+          <t>다. 준비사항 : 국별 상반기 실적과 하반기 추진계획을 7월 18일까지 영업과로 제출</t>
         </is>
       </c>
     </row>
@@ -597,27 +604,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5월 말까지 복합기 임대계약 갱신 여부 결정(6월 30일 만료)</t>
+          <t>계약소포 : 요금후납 계약업체에 발송 예정 물량을 9월 12일까지 통보하도록 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025년 5월</t>
+          <t>2025년 8월</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01_공문/05_행정지원과1720_복합기_임대계약_갱신_검토.hwpx</t>
+          <t>01_공문/06_영업과1431_202508_2025년_추석_명절_소포우편물_특별소통_대책_추진.odt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>복합기 임대계약(계약번호 HB-2023-07)이 2025년 6월 30일 만료됩니다.</t>
+          <t>다. 계약소포 : 요금후납 계약업체에 발송 예정 물량을 9월 12일까지 통보하도록 안내</t>
         </is>
       </c>
     </row>
@@ -627,28 +634,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>최우진 · 주식회사 가온복합기(가상 업체) 영업팀 · 010-0000-0505 · 복합기 임대 계약·소모품</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>조치사항 : 미납 업체에 9월 30일까지 납부를 독촉하고, 미납 시 10월부터 요금후납 발송 정지</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025년 9월</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01_공문/05_행정지원과1720_복합기_임대계약_갱신_검토.hwpx</t>
+          <t>01_공문/07_영업과1612_202509_요금후납_계약업체_우편물_발송_현황_점검_결과_보고.odt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>최우진(주식회사 가온복합기(가상 업체) 영업팀, 010-0000-0505)</t>
+          <t>나. 조치사항 : 미납 업체에 9월 30일까지 납부를 독촉하고, 미납 시 10월부터 요금후납 발송 정지</t>
         </is>
       </c>
     </row>
@@ -663,27 +674,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6월 10일~24일 개인정보 자체점검, 결과 6월 27일까지 제출</t>
+          <t>실적보고 : 기간 중 접수 실적을 1월 12일까지 영업과로 제출</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025년 6월</t>
+          <t>2025년 11월</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01_공문/06_행정지원과2015_2025년_개인정보_보호_자체점검_실시.hwpx</t>
+          <t>01_공문/09_영업과2015_202511_연말연시_우편물_특별소통기간_운영_협조_요청.odt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6월 10일부터 6월 24일까지 부서 개인정보 처리 현황을 자체점검합니다.</t>
+          <t>다. 실적보고 : 기간 중 접수 실적을 1월 12일까지 영업과로 제출</t>
         </is>
       </c>
     </row>
@@ -693,28 +704,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한서윤 · 한빛군청 정보통신과 보안담당 · 063-000-0606 · 개인정보 보호 자체점검</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>2026년도 우편매출액 목표를 붙임과 같이 배정하니 세부추진계획을 수립하여 3월 13일까지 제출하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026년 2월</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01_공문/06_행정지원과2015_2025년_개인정보_보호_자체점검_실시.hwpx</t>
+          <t>01_공문/10_우편영업과658_202602_2026년도_우편매출액_목표_배정_알림.odt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>한서윤(한빛군청 정보통신과 보안담당, 063-000-0606)</t>
+          <t>2. 2026년도 우편매출액 목표를 붙임과 같이 배정하니 세부추진계획을 수립하여 3월 13일까지 제출하여 주시기 바랍니다.</t>
         </is>
       </c>
     </row>
@@ -724,32 +739,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>협의할 사람</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7월 18일까지 2026년도 본예산 편성 요구서 제출</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025년 7월</t>
-        </is>
-      </c>
+          <t>이하람 · 가온농협 유통센터 판매담당 · 063-000-0404 · 우체국쇼핑 입점</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01_공문/07_행정지원과2301_2026년도_본예산_편성_요구서_제출.hwpx</t>
+          <t>01_공문/04_영업과812_202505_우체국쇼핑_지역특산품_입점_협의_결과_보고.odt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026년도 본예산 편성 요구서를 7월 18일까지 재정과에 제출합니다.</t>
+          <t>가. 협의업체 : 가온농협 유통센터(담당 이하람, ☎ 063-000-0404)</t>
         </is>
       </c>
     </row>
@@ -764,23 +775,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>강민재 · 한빛군청 재정과 예산담당 · 063-000-0101 · 예산 편성·추경 협의</t>
+          <t>김도현 · 가온우편집중국 발착팀 · 063-000-0202 · 소포 접수 마감시간</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01_공문/07_행정지원과2301_2026년도_본예산_편성_요구서_제출.hwpx</t>
+          <t>01_공문/06_영업과1431_202508_2025년_추석_명절_소포우편물_특별소통_대책_추진.odt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강민재(한빛군청 재정과 예산담당, 063-000-0101)</t>
+          <t>나. 창구 접수 : 접수 창구 1개 추가 운영, 소포 접수 마감시간은 집중국 발착팀과 협의(김도현, ☎ 063-000-0202)</t>
         </is>
       </c>
     </row>
@@ -790,32 +801,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>협의할 사람</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8월 냉방 26도 유지, 전기 사용량 총무과와 집계</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025년 8월</t>
-        </is>
-      </c>
+          <t>민서현 · 전북지방우정청 우편영업과 주무관 · 063-000-0101 · 우편매출 목표·세부추진계획</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01_공문/08_행정지원과2654_여름철_청사_냉방_운영_및_전기요금_절감_안내.hwpx</t>
+          <t>01_공문/10_우편영업과658_202602_2026년도_우편매출액_목표_배정_알림.odt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8월 한 달간 청사 냉방 설정 온도를 26도로 유지합니다.</t>
+          <t>※ 문의 : 우편영업과 민서현 주무관(☎ 063-000-0101)</t>
         </is>
       </c>
     </row>
@@ -825,28 +832,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>이수현 · 한빛군청 총무과 청사관리담당 · 063-000-0202 · 청사 시설·소방 점검 일정 협의</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>매월 5일까지 전월 우편매출 실적 집계 후 과장 보고</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>매월</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01_공문/08_행정지원과2654_여름철_청사_냉방_운영_및_전기요금_절감_안내.hwpx</t>
+          <t>01_공문/01_영업과412_202503_2025년_우편매출액_목표_달성_세부추진계획_수립.odt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>이수현(한빛군청 총무과 청사관리담당, 063-000-0202)</t>
+          <t>다. 진도점검 : 매월 5일까지 전월 실적을 집계하여 과장 보고</t>
         </is>
       </c>
     </row>
@@ -861,27 +872,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9월 12일까지 행정사무감사 요구자료 제출</t>
+          <t>매주 금요일 창구전시판매 매대 재고 확인·판매대장 기록, 판매대금은 익월 10일까지 정산</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025년 9월</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01_공문/09_행정지원과2980_2025년_행정사무감사_자료_제출.hwpx</t>
+          <t>01_공문/03_영업과655_202504_2025년_상반기_창구전시판매_매대_운영_계획.odt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>군의회 행정사무감사 요구자료를 9월 12일까지 의회 사무과에 제출합니다.</t>
+          <t>다. 재고점검 : 매주 금요일 매대 재고를 확인하고 판매대장에 기록</t>
         </is>
       </c>
     </row>
@@ -891,28 +902,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정하은 · 한빛군의회 사무과 · 063-000-0404 · 행정사무감사 자료 요구</t>
+          <t>요금후납 계약 2개소 발송 물량 감소로 계약 조건 재협의 필요</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01_공문/09_행정지원과2980_2025년_행정사무감사_자료_제출.hwpx</t>
+          <t>01_공문/07_영업과1612_202509_요금후납_계약업체_우편물_발송_현황_점검_결과_보고.odt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>정하은(한빛군의회 사무과, 063-000-0404)</t>
+          <t>다. 계약변경 : 2개소는 발송 물량 감소로 계약 조건 재협의 필요</t>
         </is>
       </c>
     </row>
@@ -922,32 +933,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>협의할 사람</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10월 15일까지 자체감사 지적사항(대장 누락 3건) 보완</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025년 10월</t>
-        </is>
-      </c>
+          <t>한예준 · 가온시청 홍보담당 · 063-000-0707 · 시정 홍보물 발송 계약</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01_공문/10_행정지원과3217_2025년_자체감사_지적사항_조치_계획.hwpx</t>
+          <t>02_보고서·계획(한글)/01_2025년_우편매출액_목표_달성_세부추진계획.hwpx</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>자체감사에서 지적된 소모품 구매대장 기재 누락 3건을 10월 15일까지 보완합니다.</t>
+          <t>- 가온시청 홍보담당(한예준, ☎ 063-000-0707)과 시정 홍보물 발송 계약 협의(’25.4월)</t>
         </is>
       </c>
     </row>
@@ -957,28 +964,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>윤채원 · 한빛군청 감사실 · 063-000-0808 · 자체감사 지적사항 조치</t>
+          <t>창구전시판매 매대 위치가 민원 대기석 옆이라 창구 앞으로 이동 필요</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01_공문/10_행정지원과3217_2025년_자체감사_지적사항_조치_계획.hwpx</t>
+          <t>02_보고서·계획(한글)/02_2025년_상반기_창구전시판매_운영_결과.hwpx</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>윤채원(한빛군청 감사실, 063-000-0808)</t>
+          <t>ㅇ (진열 공간) 민원 대기석 옆 매대 위치로 고객 접근이 어려워 7월 중 창구 앞으로 이동 필요</t>
         </is>
       </c>
     </row>
@@ -993,27 +1000,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11월 28일까지 기록물 정리·기록관 이관</t>
+          <t>2026년 우편매출액 세부추진계획 3월 13일까지 지방우정청 제출(목표 12,850백만원)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025년 11월</t>
+          <t>2026년 3월</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01_공문/11_행정지원과3555_2025년_기록물_정리_및_이관_계획.hwpx</t>
+          <t>02_보고서·계획(한글)/03_2026년_우편영업_업무_추진계획_초안_.hwpx</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>보존기간이 지난 기록물을 11월 28일까지 정리하여 기록관에 이관합니다.</t>
+          <t>ㅇ (목표) 12,850백만원(전년 比 3.0% 증), 세부추진계획 3월 13일까지 지방우정청 제출</t>
         </is>
       </c>
     </row>
@@ -1023,28 +1030,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>문지호 · 전북특별자치도 자치행정과(가상 부서명) · 063-000-0707 · 기록물 이관 지침 문의</t>
+          <t>요금후납 계약은 만료 2개월 전 갱신 안내, 미납 업체 월별 점검</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01_공문/11_행정지원과3555_2025년_기록물_정리_및_이관_계획.hwpx</t>
+          <t>02_보고서·계획(한글)/03_2026년_우편영업_업무_추진계획_초안_.hwpx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>문지호(전북특별자치도 자치행정과(가상 부서명), 063-000-0707)</t>
+          <t>ㅇ (계약 관리) 만료 2개월 전 요금후납 계약 갱신 안내, 미납 업체 월별 점검</t>
         </is>
       </c>
     </row>
@@ -1054,32 +1061,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12월 8일~12일 재물조사, 결과 12월 19일까지 제출</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025년 12월</t>
-        </is>
-      </c>
+          <t>(주)한결물류 미납 요금 분할납부 협의 미완료, 매대 가온배 재고 12개 반품 협의 중</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01_공문/12_행정지원과3890_연말_재물조사_실시_계획.hwpx</t>
+          <t>02_보고서·계획(한글)/03_2026년_우편영업_업무_추진계획_초안_.hwpx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12월 8일부터 12월 12일까지 부서 비품 재물조사를 실시합니다.</t>
+          <t>ㅇ (미결 사항) (주)한결물류 미납 요금 분할납부 협의 미완료, 매대 가온배 재고 12개 반품 협의 중</t>
         </is>
       </c>
     </row>
@@ -1094,23 +1097,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>강민재 · 한빛군청 재정과 예산담당 · 063-000-0101 · 예산 편성·추경 협의</t>
+          <t>박세진 · (주)한결물류 발송담당 · 010-0000-0303 · 요금후납 계약·미납 요금</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>01_공문/12_행정지원과3890_연말_재물조사_실시_계획.hwpx</t>
+          <t>03_대장·현황(엑셀)/요금후납_계약현황.xlsx</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>2행</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>강민재(한빛군청 재정과 예산담당, 063-000-0101)</t>
+          <t>박세진</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1128,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1월 말까지 상반기 소방안전점검 일정 사전 협의</t>
+          <t>가온시청 요금후납 계약 2026-02-28 만료, 갱신 안내(만료 2개월 전)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026년 1월</t>
+          <t>2025년 12월</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01_공문/13_행정지원과0112_2026년_상반기_청사_소방안전점검_사전_협의.hwpx</t>
+          <t>03_대장·현황(엑셀)/요금후납_계약현황.xlsx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>3행</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026년 상반기 소방안전점검은 4월 중 실시 예정이며 1월 말까지 소방서와 일정을 사전 협의합니다.</t>
+          <t>2024-03-01~2026-02-28</t>
         </is>
       </c>
     </row>
@@ -1155,28 +1158,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>박도윤 · 한빛소방서 예방안전과 · 063-000-0303 · 소방안전점검 입회</t>
+          <t>2025년 우편매출액 누계 달성률 96.3%로 목표 미달(소포 부문)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01_공문/13_행정지원과0112_2026년_상반기_청사_소방안전점검_사전_협의.hwpx</t>
+          <t>03_대장·현황(엑셀)/우편매출액_월별실적_2025.xlsx</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>14행</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>박도윤(한빛소방서 예방안전과, 063-000-0303)</t>
+          <t>96.3%</t>
         </is>
       </c>
     </row>
@@ -1186,32 +1189,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>협의할 사람</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2월 20일까지 2026년 사무관리비 집행 계획 수립</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026년 2월</t>
-        </is>
-      </c>
+          <t>정윤서 · 가온남부우체국 창구팀장 · 063-000-0505 · 진도점검 회의 간사</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01_공문/14_행정지원과0455_2026년_사무관리비_집행_계획_수립.hwpx</t>
+          <t>03_대장·현황(엑셀)/관내국_연락처.xlsx</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>2행</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026년 사무관리비 집행 계획을 2월 20일까지 수립합니다.</t>
+          <t>정윤서</t>
         </is>
       </c>
     </row>
@@ -1221,28 +1220,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>강민재 · 한빛군청 재정과 예산담당 · 063-000-0101 · 예산 편성·추경 협의</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>요금후납 미납 요금은 익월 말까지 납부 독촉, 2개월 미납 시 발송 정지</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>익월</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>01_공문/14_행정지원과0455_2026년_사무관리비_집행_계획_수립.hwpx</t>
+          <t>04_매뉴얼·회의록(워드)/우편영업실_업무매뉴얼_초안.docx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>구역 1</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>강민재(한빛군청 재정과 예산담당, 063-000-0101)</t>
+          <t>나. 미납 요금이 있으면 익월 말까지 납부를 독촉하고, 2개월 미납 시 발송을 정지한다.</t>
         </is>
       </c>
     </row>
@@ -1252,28 +1255,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>최우진 · 주식회사 가온복합기(가상 업체) 영업팀 · 010-0000-0505 · 복합기 임대 계약·소모품</t>
+          <t>(주)한결물류 7월분 요금 1,240천원 미납, 2회 분할 납부 요청</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02_대장·현황(엑셀)/계약_현황.xlsx</t>
+          <t>04_매뉴얼·회의록(워드)/영업과_주간회의록_20251110.docx</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>시트 「계약」</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>최우진 010-0000-0505</t>
+          <t>(주)한결물류 7월분 1,240천원이 아직 미납 상태이며, 업체는 2회 분할 납부를 요청하였다.</t>
         </is>
       </c>
     </row>
@@ -1283,32 +1286,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>진행 중 현안</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>예산 집행률 저조: 2025년 12월 기준 사무관리비 집행률이 71%로 목표에 미달합니다.</t>
+          <t>11월 말까지 분할 납부 합의서 접수, 미합의 시 12월부터 발송 정지</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025년 12월</t>
+          <t>2025년 11월</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02_대장·현황(엑셀)/예산집행현황_2025.xlsx</t>
+          <t>04_매뉴얼·회의록(워드)/영업과_주간회의록_20251110.docx</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>시트 「집행」</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>과장 지시: 11월 말까지 분할 납부 합의서를 받고, 합의가 안 되면 12월부터 발송을 정지한다.</t>
         </is>
       </c>
     </row>
@@ -1323,27 +1326,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>임대·용역 계약은 만료 2개월 전에 갱신 여부 검토(상시)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>상시</t>
-        </is>
-      </c>
+          <t>우수사례 제출 자료는 제출 1주 전 과장 검토</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>03_계획·매뉴얼(워드)/서무_업무매뉴얼_초안.docx</t>
+          <t>04_매뉴얼·회의록(워드)/인수인계서_2024_전전임자.docx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>문단 6</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>임대·용역 계약은 만료 2개월 전에 갱신 여부를 검토한다.</t>
+          <t>3. 유의사항: 우수사례 제출 자료는 제출 1주 전 과장 검토를 받을 것</t>
         </is>
       </c>
     </row>
@@ -1358,27 +1357,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>자체감사 지적사항 1건 미조치: 소모품 구매대장 누락 3건 중 1건은 영수증을 찾지 못해 미조치 상태입니다.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025년 10월~</t>
-        </is>
-      </c>
+          <t>우수사례 제출 서식 반려(성과 수치 누락), 10월 17일까지 재제출</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>03_계획·매뉴얼(워드)/과_업무회의_회의록_202510.docx</t>
+          <t>05_메일/20251014_우수사례_재제출_요청.eml</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>문단 6</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1건은 영수증을 찾지 못해 미조치 상태입니다.</t>
+          <t>보내주신 우수사례 서식에 성과 수치(판매액·입점 품목 수)가 빠져 있어 반려합니다.</t>
         </is>
       </c>
     </row>
@@ -1388,32 +1383,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소모품 구매대장 월 1회 점검(매월 말)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>매월</t>
-        </is>
-      </c>
+          <t>(주)한결물류가 미납 요금 1,240천원을 12월·1월 2회 분할 납부 요청, 회신 필요</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03_계획·매뉴얼(워드)/2026_서무업무_추진계획안.docx</t>
+          <t>05_메일/20251120_한결물류_분할납부_요청.eml</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>문단 4</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>소모품 구매대장 월 1회 점검(매월 말)</t>
+          <t>7월분 미납 요금 1,240천원을 12월과 1월 두 번에 나누어 납부하고자 합니다.</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1414,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>월별 할 일</t>
+          <t>진행 중 현안</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>행정사무감사 자료는 제출 1주 전 과장 검토</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025년 9월</t>
-        </is>
-      </c>
+          <t>(주)한결물류 분할납부 합의서 미접수, 1월 말까지 못 받으면 발송 정지 공문</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>06_기타/인수인계서_2024_전전임자.pdf</t>
+          <t>06_메모/메모_한결물류.txt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1쪽</t>
+          <t>3행</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>제출 1주 전 과장 검토를 받을 것</t>
+          <t>12.3 업체 통화, 합의서 아직 안 옴.</t>
         </is>
       </c>
     </row>
@@ -1463,27 +1450,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>기록물 이관 목록 반려: 기록관에서 이관 목록 서식 오류로 반려되어 재작성이 필요합니다.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025년 11월</t>
-        </is>
-      </c>
+          <t>매대 가온배 재고 12개(유통기한 2026.2.28) 반품 불가, 2월 중 교환·할인 결정 필요</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>04_메일/20251120_기록물_이관목록_반려.eml</t>
+          <t>06_메모/메모_매대.txt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>3행</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서식 오류(보존기간 열 누락)로 반려되었습니다</t>
+          <t>농협 이하람 담당에게 반품 요청(1.15). "반품은 어렵고 교환은 가능"이라 함. 결론 못 냄.</t>
         </is>
       </c>
     </row>
@@ -1493,28 +1476,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>협의할 사람</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>신가상 · 한빛군청 기록관 · 063-000-1111 · 기록물 이관 목록</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>가온시청 요금후납 계약 갱신 신청서 접수(2026.2.28 만료)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026년 2월</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>04_메일/20251120_기록물_이관목록_반려.eml</t>
+          <t>06_메모/할일.md</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>3행</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>신가상 063-000-1111</t>
+          <t>가온시청 계약 갱신 신청서 접수(2.28 만료)</t>
         </is>
       </c>
     </row>
@@ -1524,595 +1511,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>진행 중 현안</t>
+          <t>월별 할 일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>복합기 임대계약 갱신 미결: 업체가 월 임대료 195,000원을 요구하여 협의가 끝나지 않았습니다.</t>
+          <t>우수사례 수치 보완본 재제출(10월 16일)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026년 1월</t>
+          <t>2025년 10월</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>04_메일/20260114_복합기_임대료_협의.eml</t>
+          <t>07_기타/2025_우수사례_제출자료.zip ▸ 제출목록.txt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>4행</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>월 임대료 195,000원입니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>진행 중 현안</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>복합기 임대계약 2026년 2월 안에 갱신 결정 필요(업체 195,000원 요구, 증액 3% 이내 원칙)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026년 2월</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>05_메모/메모_복합기계약.txt</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>후임자가 2월 안에 결정해야 함</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>진행 중 현안</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>청사 2층 복도 누수: 2026년 1월부터 2층 복도 천장 누수가 반복되어 총무과에 보수를 요청해 두었습니다.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026년 1월~</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>05_메모/메모_누수.txt</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>아직 보수 안 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>월별 할 일</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>행정사무감사 자료 3종(집행내역·계약 현황·구매대장) 9월 제출</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025년 9월</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>06_기타/행감_제출자료_2025.zip ▸ 제출목록.txt</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>제출일 2025-09-11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>읽기 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01_공문/03_행정지원과1023_2025년_상반기_소모품_구매_계획_수립.hwpx</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01_공문/04_행정지원과1388_2025년_청사_소방안전점검_실시_계획.hwpx</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>01_공문/05_행정지원과1720_복합기_임대계약_갱신_검토.hwpx</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>01_공문/06_행정지원과2015_2025년_개인정보_보호_자체점검_실시.hwpx</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>01_공문/07_행정지원과2301_2026년도_본예산_편성_요구서_제출.hwpx</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>01_공문/08_행정지원과2654_여름철_청사_냉방_운영_및_전기요금_절감_안내.hwpx</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>01_공문/09_행정지원과2980_2025년_행정사무감사_자료_제출.hwpx</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>01_공문/10_행정지원과3217_2025년_자체감사_지적사항_조치_계획.hwpx</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>01_공문/11_행정지원과3555_2025년_기록물_정리_및_이관_계획.hwpx</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>01_공문/12_행정지원과3890_연말_재물조사_실시_계획.hwpx</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>01_공문/13_행정지원과0112_2026년_상반기_청사_소방안전점검_사전_협의.hwpx</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>01_공문/14_행정지원과0455_2026년_사무관리비_집행_계획_수립.hwpx</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>02_대장·현황(엑셀)/연간_업무일정표_2025.xlsx</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>02_대장·현황(엑셀)/소모품_구매대장_2025.xlsx</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>02_대장·현황(엑셀)/계약_현황.xlsx</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>02_대장·현황(엑셀)/업무_연락처(가상).xlsx</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02_대장·현황(엑셀)/예산집행현황_2025.xlsx</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>03_계획·매뉴얼(워드)/서무_업무매뉴얼_초안.docx</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03_계획·매뉴얼(워드)/과_업무회의_회의록_202510.docx</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>03_계획·매뉴얼(워드)/인수인계서_2024_전전임자.docx</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03_계획·매뉴얼(워드)/2026_서무업무_추진계획안.docx</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>06_기타/서무_업무매뉴얼_초안.pdf</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>06_기타/인수인계서_2024_전전임자.pdf</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>06_기타/2026_서무업무_추진계획안.pdf</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>04_메일/20251120_기록물_이관목록_반려.eml</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>04_메일/20250603_개인정보_자체점검표_배포.eml</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>04_메일/20260114_복합기_임대료_협의.eml</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>04_메일/20250901_행감자료_요구.eml</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>05_메모/메모_복합기계약.txt</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>05_메모/메모_누수.txt</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>05_메모/연간_할일_체크.md</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>05_메모/메모_기타.txt</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>06_기타/행감_제출자료_2025.zip</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>06_기타/옛공문_스캔.jpg</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>아니요(의도된 불량 파일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>06_기타/손상된_문서.hwp</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>아니요(의도된 불량 파일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>06_기타/암호걸린_안내문.pdf</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>아니요(의도된 불량 파일)</t>
+          <t>재제출일 2025-10-16</t>
         </is>
       </c>
     </row>

--- a/바통/돌다리/모의데이터/정답표.xlsx
+++ b/바통/돌다리/모의데이터/정답표.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>박세진</t>
+          <t>박세진	010-0000-0303</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>정윤서</t>
+          <t>정윤서	063-000-0505</t>
         </is>
       </c>
     </row>
